--- a/plantillas/1_conceptos.xlsx
+++ b/plantillas/1_conceptos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USUARIO\Documentos\GitHub\sistema-importaciones1\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3916C7D5-27BE-4889-99B8-AEC5BB32C1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30323AF-85D0-4C79-BF8C-1544749BB1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{80D3F11C-FFF1-412E-92CE-ADF8A4544162}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80D3F11C-FFF1-412E-92CE-ADF8A4544162}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
